--- a/data/signal_backtest.xlsx
+++ b/data/signal_backtest.xlsx
@@ -450,7 +450,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>190115</v>
+        <v>191953</v>
       </c>
       <c r="C2" t="n">
         <v>14.5</v>
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1307</v>
+        <v>1318</v>
       </c>
       <c r="C3" t="n">
         <v>35.6</v>
@@ -484,7 +484,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="C4" t="n">
         <v>20.8</v>
@@ -501,13 +501,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4138</v>
+        <v>4169</v>
       </c>
       <c r="C5" t="n">
         <v>32.2</v>
       </c>
       <c r="D5" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="E5" t="inlineStr"/>
     </row>
@@ -518,10 +518,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>19309</v>
+        <v>19488</v>
       </c>
       <c r="C6" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="D6" t="n">
         <v>1.63</v>
@@ -535,13 +535,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10685</v>
+        <v>10794</v>
       </c>
       <c r="C7" t="n">
         <v>26.8</v>
       </c>
       <c r="D7" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="E7" t="inlineStr"/>
     </row>
@@ -552,13 +552,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5396</v>
+        <v>5452</v>
       </c>
       <c r="C8" t="n">
-        <v>30.4</v>
+        <v>30.5</v>
       </c>
       <c r="D8" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="E8" t="inlineStr"/>
     </row>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="C9" t="n">
         <v>29.2</v>
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>555</v>
+        <v>561</v>
       </c>
       <c r="C10" t="n">
-        <v>43.4</v>
+        <v>43.5</v>
       </c>
       <c r="D10" t="n">
         <v>2.99</v>

--- a/data/signal_backtest.xlsx
+++ b/data/signal_backtest.xlsx
@@ -450,7 +450,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>191953</v>
+        <v>193327</v>
       </c>
       <c r="C2" t="n">
         <v>14.5</v>
@@ -467,13 +467,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1318</v>
+        <v>1325</v>
       </c>
       <c r="C3" t="n">
-        <v>35.6</v>
+        <v>35.5</v>
       </c>
       <c r="D3" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="E3" t="inlineStr"/>
     </row>
@@ -484,13 +484,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C4" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="D4" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="E4" t="inlineStr"/>
     </row>
@@ -501,13 +501,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4169</v>
+        <v>4196</v>
       </c>
       <c r="C5" t="n">
         <v>32.2</v>
       </c>
       <c r="D5" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="E5" t="inlineStr"/>
     </row>
@@ -518,7 +518,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>19488</v>
+        <v>19626</v>
       </c>
       <c r="C6" t="n">
         <v>23.7</v>
@@ -535,13 +535,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10794</v>
+        <v>10882</v>
       </c>
       <c r="C7" t="n">
         <v>26.8</v>
       </c>
       <c r="D7" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="E7" t="inlineStr"/>
     </row>
@@ -552,7 +552,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5452</v>
+        <v>5496</v>
       </c>
       <c r="C8" t="n">
         <v>30.5</v>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C9" t="n">
-        <v>29.2</v>
+        <v>29.1</v>
       </c>
       <c r="D9" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="E9" t="inlineStr"/>
     </row>
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="C10" t="n">
-        <v>43.5</v>
+        <v>43.4</v>
       </c>
       <c r="D10" t="n">
         <v>2.99</v>

--- a/data/signal_backtest.xlsx
+++ b/data/signal_backtest.xlsx
@@ -450,10 +450,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>193327</v>
+        <v>194936</v>
       </c>
       <c r="C2" t="n">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1325</v>
+        <v>1332</v>
       </c>
       <c r="C3" t="n">
         <v>35.5</v>
@@ -484,13 +484,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="C4" t="n">
-        <v>20.7</v>
+        <v>20.5</v>
       </c>
       <c r="D4" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="E4" t="inlineStr"/>
     </row>
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4196</v>
+        <v>4219</v>
       </c>
       <c r="C5" t="n">
         <v>32.2</v>
@@ -518,10 +518,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>19626</v>
+        <v>19759</v>
       </c>
       <c r="C6" t="n">
-        <v>23.7</v>
+        <v>23.8</v>
       </c>
       <c r="D6" t="n">
         <v>1.63</v>
@@ -535,10 +535,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10882</v>
+        <v>10968</v>
       </c>
       <c r="C7" t="n">
-        <v>26.8</v>
+        <v>26.9</v>
       </c>
       <c r="D7" t="n">
         <v>1.84</v>
@@ -552,13 +552,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5496</v>
+        <v>5535</v>
       </c>
       <c r="C8" t="n">
         <v>30.5</v>
       </c>
       <c r="D8" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="E8" t="inlineStr"/>
     </row>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C9" t="n">
         <v>29.1</v>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="E9" t="inlineStr"/>
     </row>
@@ -586,13 +586,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="C10" t="n">
-        <v>43.4</v>
+        <v>43.3</v>
       </c>
       <c r="D10" t="n">
-        <v>2.99</v>
+        <v>2.97</v>
       </c>
       <c r="E10" t="inlineStr"/>
     </row>

--- a/data/signal_backtest.xlsx
+++ b/data/signal_backtest.xlsx
@@ -450,7 +450,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>194936</v>
+        <v>195998</v>
       </c>
       <c r="C2" t="n">
         <v>14.6</v>
@@ -467,13 +467,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1332</v>
+        <v>1338</v>
       </c>
       <c r="C3" t="n">
         <v>35.5</v>
       </c>
       <c r="D3" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="E3" t="inlineStr"/>
     </row>
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4219</v>
+        <v>4239</v>
       </c>
       <c r="C5" t="n">
         <v>32.2</v>
@@ -518,7 +518,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>19759</v>
+        <v>19849</v>
       </c>
       <c r="C6" t="n">
         <v>23.8</v>
@@ -535,10 +535,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10968</v>
+        <v>11008</v>
       </c>
       <c r="C7" t="n">
-        <v>26.9</v>
+        <v>27</v>
       </c>
       <c r="D7" t="n">
         <v>1.84</v>
@@ -552,13 +552,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5535</v>
+        <v>5560</v>
       </c>
       <c r="C8" t="n">
-        <v>30.5</v>
+        <v>30.6</v>
       </c>
       <c r="D8" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="E8" t="inlineStr"/>
     </row>
@@ -586,13 +586,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="C10" t="n">
         <v>43.3</v>
       </c>
       <c r="D10" t="n">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
       <c r="E10" t="inlineStr"/>
     </row>

--- a/data/signal_backtest.xlsx
+++ b/data/signal_backtest.xlsx
@@ -450,10 +450,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>195998</v>
+        <v>197468</v>
       </c>
       <c r="C2" t="n">
-        <v>14.6</v>
+        <v>14.7</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
@@ -467,13 +467,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1338</v>
+        <v>1344</v>
       </c>
       <c r="C3" t="n">
-        <v>35.5</v>
+        <v>35.4</v>
       </c>
       <c r="D3" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="E3" t="inlineStr"/>
     </row>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C4" t="n">
-        <v>20.5</v>
+        <v>20.7</v>
       </c>
       <c r="D4" t="n">
         <v>1.41</v>
@@ -501,13 +501,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4239</v>
+        <v>4260</v>
       </c>
       <c r="C5" t="n">
-        <v>32.2</v>
+        <v>32.3</v>
       </c>
       <c r="D5" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="E5" t="inlineStr"/>
     </row>
@@ -518,7 +518,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>19849</v>
+        <v>19962</v>
       </c>
       <c r="C6" t="n">
         <v>23.8</v>
@@ -535,10 +535,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>11008</v>
+        <v>11065</v>
       </c>
       <c r="C7" t="n">
-        <v>27</v>
+        <v>26.9</v>
       </c>
       <c r="D7" t="n">
         <v>1.84</v>
@@ -552,13 +552,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5560</v>
+        <v>5582</v>
       </c>
       <c r="C8" t="n">
         <v>30.6</v>
       </c>
       <c r="D8" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="E8" t="inlineStr"/>
     </row>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="C9" t="n">
-        <v>29.1</v>
+        <v>28.9</v>
       </c>
       <c r="D9" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="E9" t="inlineStr"/>
     </row>
@@ -586,7 +586,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="C10" t="n">
         <v>43.3</v>

--- a/data/signal_backtest.xlsx
+++ b/data/signal_backtest.xlsx
@@ -450,7 +450,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>197468</v>
+        <v>198940</v>
       </c>
       <c r="C2" t="n">
         <v>14.7</v>
@@ -467,13 +467,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1344</v>
+        <v>1350</v>
       </c>
       <c r="C3" t="n">
-        <v>35.4</v>
+        <v>35.5</v>
       </c>
       <c r="D3" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="E3" t="inlineStr"/>
     </row>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="C4" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="D4" t="n">
         <v>1.41</v>
@@ -501,10 +501,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4260</v>
+        <v>4282</v>
       </c>
       <c r="C5" t="n">
-        <v>32.3</v>
+        <v>32.4</v>
       </c>
       <c r="D5" t="n">
         <v>2.2</v>
@@ -518,13 +518,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>19962</v>
+        <v>20146</v>
       </c>
       <c r="C6" t="n">
         <v>23.8</v>
       </c>
       <c r="D6" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="E6" t="inlineStr"/>
     </row>
@@ -535,10 +535,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>11065</v>
+        <v>11154</v>
       </c>
       <c r="C7" t="n">
-        <v>26.9</v>
+        <v>27</v>
       </c>
       <c r="D7" t="n">
         <v>1.84</v>
@@ -552,10 +552,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5582</v>
+        <v>5618</v>
       </c>
       <c r="C8" t="n">
-        <v>30.6</v>
+        <v>30.8</v>
       </c>
       <c r="D8" t="n">
         <v>2.09</v>
@@ -575,7 +575,7 @@
         <v>28.9</v>
       </c>
       <c r="D9" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="E9" t="inlineStr"/>
     </row>
@@ -586,13 +586,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="C10" t="n">
-        <v>43.3</v>
+        <v>43.4</v>
       </c>
       <c r="D10" t="n">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="E10" t="inlineStr"/>
     </row>

--- a/data/signal_backtest.xlsx
+++ b/data/signal_backtest.xlsx
@@ -450,7 +450,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>198940</v>
+        <v>200215</v>
       </c>
       <c r="C2" t="n">
         <v>14.7</v>
@@ -467,13 +467,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1350</v>
+        <v>1355</v>
       </c>
       <c r="C3" t="n">
-        <v>35.5</v>
+        <v>35.6</v>
       </c>
       <c r="D3" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="E3" t="inlineStr"/>
     </row>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C4" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="D4" t="n">
         <v>1.41</v>
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4282</v>
+        <v>4299</v>
       </c>
       <c r="C5" t="n">
         <v>32.4</v>
@@ -518,7 +518,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20146</v>
+        <v>20249</v>
       </c>
       <c r="C6" t="n">
         <v>23.8</v>
@@ -535,13 +535,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>11154</v>
+        <v>11203</v>
       </c>
       <c r="C7" t="n">
         <v>27</v>
       </c>
       <c r="D7" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="E7" t="inlineStr"/>
     </row>
@@ -552,7 +552,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5618</v>
+        <v>5639</v>
       </c>
       <c r="C8" t="n">
         <v>30.8</v>
@@ -586,7 +586,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="C10" t="n">
         <v>43.4</v>

--- a/data/signal_backtest.xlsx
+++ b/data/signal_backtest.xlsx
@@ -450,7 +450,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>200215</v>
+        <v>201896</v>
       </c>
       <c r="C2" t="n">
         <v>14.7</v>
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1355</v>
+        <v>1358</v>
       </c>
       <c r="C3" t="n">
         <v>35.6</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C4" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="D4" t="n">
         <v>1.41</v>
@@ -501,13 +501,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4299</v>
+        <v>4320</v>
       </c>
       <c r="C5" t="n">
         <v>32.4</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="E5" t="inlineStr"/>
     </row>
@@ -518,7 +518,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20249</v>
+        <v>20406</v>
       </c>
       <c r="C6" t="n">
         <v>23.8</v>
@@ -535,10 +535,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>11203</v>
+        <v>11284</v>
       </c>
       <c r="C7" t="n">
-        <v>27</v>
+        <v>26.9</v>
       </c>
       <c r="D7" t="n">
         <v>1.83</v>
@@ -552,10 +552,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5639</v>
+        <v>5676</v>
       </c>
       <c r="C8" t="n">
-        <v>30.8</v>
+        <v>30.7</v>
       </c>
       <c r="D8" t="n">
         <v>2.09</v>
@@ -575,7 +575,7 @@
         <v>28.9</v>
       </c>
       <c r="D9" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="E9" t="inlineStr"/>
     </row>
@@ -592,7 +592,7 @@
         <v>43.4</v>
       </c>
       <c r="D10" t="n">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="E10" t="inlineStr"/>
     </row>

--- a/data/signal_backtest.xlsx
+++ b/data/signal_backtest.xlsx
@@ -450,7 +450,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>201896</v>
+        <v>203379</v>
       </c>
       <c r="C2" t="n">
         <v>14.7</v>
@@ -467,10 +467,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1358</v>
+        <v>1362</v>
       </c>
       <c r="C3" t="n">
-        <v>35.6</v>
+        <v>35.5</v>
       </c>
       <c r="D3" t="n">
         <v>2.42</v>
@@ -484,13 +484,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C4" t="n">
         <v>20.6</v>
       </c>
       <c r="D4" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="E4" t="inlineStr"/>
     </row>
@@ -501,13 +501,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4320</v>
+        <v>4335</v>
       </c>
       <c r="C5" t="n">
-        <v>32.4</v>
+        <v>32.3</v>
       </c>
       <c r="D5" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="E5" t="inlineStr"/>
     </row>
@@ -518,10 +518,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20406</v>
+        <v>20536</v>
       </c>
       <c r="C6" t="n">
-        <v>23.8</v>
+        <v>23.7</v>
       </c>
       <c r="D6" t="n">
         <v>1.62</v>
@@ -535,7 +535,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>11284</v>
+        <v>11356</v>
       </c>
       <c r="C7" t="n">
         <v>26.9</v>
@@ -552,13 +552,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5676</v>
+        <v>5709</v>
       </c>
       <c r="C8" t="n">
-        <v>30.7</v>
+        <v>30.6</v>
       </c>
       <c r="D8" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="E8" t="inlineStr"/>
     </row>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C9" t="n">
-        <v>28.9</v>
+        <v>28.7</v>
       </c>
       <c r="D9" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="E9" t="inlineStr"/>
     </row>
@@ -592,7 +592,7 @@
         <v>43.4</v>
       </c>
       <c r="D10" t="n">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="E10" t="inlineStr"/>
     </row>
